--- a/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
+++ b/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS PERSONALES\PRESUPUESTO_GASTOS\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F28E3-5106-4220-BD69-45EE71A54927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CF9537-A705-4C80-BD70-EB92589C1AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2299,72 +2299,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -2412,236 +2347,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7257,10 +6962,10 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="48" customWidth="1"/>
-    <col min="10" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="10" max="11" width="16" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="16" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="42" customWidth="1"/>
   </cols>
@@ -7498,7 +7203,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="3"/>
       <c r="P7" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q7" s="1"/>
     </row>
@@ -7539,7 +7244,7 @@
       <c r="N8" s="6"/>
       <c r="O8" s="3"/>
       <c r="P8" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q8" s="1"/>
     </row>
@@ -7580,7 +7285,7 @@
       <c r="N9" s="6"/>
       <c r="O9" s="3"/>
       <c r="P9" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q9" s="1"/>
     </row>
@@ -11900,25 +11605,25 @@
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="P5:P40">
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>P5="Bloqueado"</formula>
+  <conditionalFormatting sqref="A5:O5">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>A5="Bloqueado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="13">
-      <formula>P5="En progreso"</formula>
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>A5="En progreso"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:Q4010">
-    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="11" stopIfTrue="1">
       <formula>A5="Completado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:O5">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>A5="Bloqueado"</formula>
+  <conditionalFormatting sqref="P5:P40">
+    <cfRule type="expression" dxfId="1" priority="12">
+      <formula>P5="Bloqueado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>A5="En progreso"</formula>
+    <cfRule type="expression" dxfId="0" priority="13">
+      <formula>P5="En progreso"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
+++ b/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS PERSONALES\PRESUPUESTO_GASTOS\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CF9537-A705-4C80-BD70-EB92589C1AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6A57AB-BC5B-410B-932A-51CD8851965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7326,7 +7326,7 @@
       <c r="N10" s="6"/>
       <c r="O10" s="3"/>
       <c r="P10" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q10" s="1"/>
     </row>
@@ -7367,7 +7367,7 @@
       <c r="N11" s="6"/>
       <c r="O11" s="3"/>
       <c r="P11" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q11" s="1"/>
     </row>

--- a/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
+++ b/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS PERSONALES\PRESUPUESTO_GASTOS\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6A57AB-BC5B-410B-932A-51CD8851965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C46EF75-9F75-4307-82F5-D73F3991B530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7408,7 +7408,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="3"/>
       <c r="P12" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q12" s="1"/>
     </row>
@@ -7449,7 +7449,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="3"/>
       <c r="P13" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q13" s="1"/>
     </row>
@@ -7490,7 +7490,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="3"/>
       <c r="P14" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q14" s="1"/>
     </row>
@@ -7531,7 +7531,7 @@
       <c r="N15" s="6"/>
       <c r="O15" s="3"/>
       <c r="P15" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q15" s="1"/>
     </row>
@@ -7572,7 +7572,7 @@
       <c r="N16" s="6"/>
       <c r="O16" s="3"/>
       <c r="P16" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q16" s="1"/>
     </row>
@@ -7613,7 +7613,7 @@
       <c r="N17" s="6"/>
       <c r="O17" s="3"/>
       <c r="P17" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q17" s="1"/>
     </row>
@@ -7654,7 +7654,7 @@
       <c r="N18" s="6"/>
       <c r="O18" s="3"/>
       <c r="P18" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q18" s="1"/>
     </row>

--- a/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
+++ b/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS PERSONALES\PRESUPUESTO_GASTOS\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C46EF75-9F75-4307-82F5-D73F3991B530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A830D36E-84BD-41C9-A77E-3C61CA8987B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7695,7 +7695,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="3"/>
       <c r="P19" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q19" s="1"/>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="N20" s="6"/>
       <c r="O20" s="3"/>
       <c r="P20" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q20" s="1"/>
     </row>
@@ -7777,7 +7777,7 @@
       <c r="N21" s="6"/>
       <c r="O21" s="3"/>
       <c r="P21" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q21" s="1"/>
     </row>
@@ -7818,7 +7818,7 @@
       <c r="N22" s="6"/>
       <c r="O22" s="3"/>
       <c r="P22" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q22" s="1"/>
     </row>
@@ -7859,7 +7859,7 @@
       <c r="N23" s="6"/>
       <c r="O23" s="3"/>
       <c r="P23" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q23" s="1"/>
     </row>
@@ -7900,7 +7900,7 @@
       <c r="N24" s="6"/>
       <c r="O24" s="3"/>
       <c r="P24" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q24" s="1"/>
     </row>
@@ -7941,7 +7941,7 @@
       <c r="N25" s="6"/>
       <c r="O25" s="3"/>
       <c r="P25" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q25" s="1"/>
     </row>
@@ -7982,7 +7982,7 @@
       <c r="N26" s="6"/>
       <c r="O26" s="3"/>
       <c r="P26" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q26" s="1"/>
     </row>
@@ -8023,7 +8023,7 @@
       <c r="N27" s="6"/>
       <c r="O27" s="3"/>
       <c r="P27" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q27" s="1"/>
     </row>
@@ -8064,7 +8064,7 @@
       <c r="N28" s="6"/>
       <c r="O28" s="3"/>
       <c r="P28" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q28" s="1"/>
     </row>

--- a/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
+++ b/docs/BITACORA_presupuesto_costos_app_MVP_actualizada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS PERSONALES\PRESUPUESTO_GASTOS\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A830D36E-84BD-41C9-A77E-3C61CA8987B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E31041-D594-4C73-A6B8-0D7B05D4AFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8105,7 +8105,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="3"/>
       <c r="P29" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q29" s="1"/>
     </row>
@@ -8146,7 +8146,7 @@
       <c r="N30" s="6"/>
       <c r="O30" s="3"/>
       <c r="P30" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q30" s="1"/>
     </row>
@@ -8187,7 +8187,7 @@
       <c r="N31" s="6"/>
       <c r="O31" s="3"/>
       <c r="P31" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q31" s="1"/>
     </row>
@@ -8228,7 +8228,7 @@
       <c r="N32" s="6"/>
       <c r="O32" s="3"/>
       <c r="P32" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q32" s="1"/>
     </row>
@@ -8269,7 +8269,7 @@
       <c r="N33" s="6"/>
       <c r="O33" s="3"/>
       <c r="P33" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q33" s="1"/>
     </row>
@@ -8310,7 +8310,7 @@
       <c r="N34" s="6"/>
       <c r="O34" s="3"/>
       <c r="P34" s="1" t="s">
-        <v>406</v>
+        <v>671</v>
       </c>
       <c r="Q34" s="1"/>
     </row>
